--- a/booking.xlsx
+++ b/booking.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ATS\crm_house\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7AF46C8-8A25-49F0-899B-6D481596D201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EF0390B-A2B5-4D60-9D2C-9360EA730D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D9B1116C-A23B-4F7B-8FBF-BBA33CFC25B0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="698">
   <si>
     <t>Sotildi</t>
   </si>
@@ -2126,13 +2126,16 @@
   </si>
   <si>
     <t>description</t>
+  </si>
+  <si>
+    <t>Bino</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2186,8 +2189,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2222,6 +2232,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -2302,7 +2318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2331,7 +2347,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2373,6 +2389,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2720,7 +2739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E987B6-1276-4D84-83C3-2F672E3C8C43}">
-  <dimension ref="A1:N221"/>
+  <dimension ref="A1:O221"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" customWidth="1"/>
@@ -2736,9 +2755,10 @@
     <col min="12" max="12" width="18.88671875" customWidth="1"/>
     <col min="13" max="13" width="10.21875" customWidth="1"/>
     <col min="14" max="14" width="10.44140625" customWidth="1"/>
+    <col min="15" max="15" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>683</v>
       </c>
@@ -2781,8 +2801,11 @@
       <c r="N1" s="9" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="28" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2812,8 +2835,11 @@
       </c>
       <c r="M2" s="26"/>
       <c r="N2" s="26"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2839,8 +2865,11 @@
       </c>
       <c r="M3" s="26"/>
       <c r="N3" s="26"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2866,8 +2895,11 @@
       </c>
       <c r="M4" s="26"/>
       <c r="N4" s="26"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2893,8 +2925,11 @@
       </c>
       <c r="M5" s="26"/>
       <c r="N5" s="26"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2920,10 +2955,15 @@
       <c r="K6" t="s">
         <v>428</v>
       </c>
-      <c r="M6" s="26"/>
+      <c r="M6" s="26" t="s">
+        <v>182</v>
+      </c>
       <c r="N6" s="26"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2951,8 +2991,11 @@
       </c>
       <c r="M7" s="26"/>
       <c r="N7" s="26"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2980,8 +3023,11 @@
       </c>
       <c r="M8" s="26"/>
       <c r="N8" s="26"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3012,8 +3058,11 @@
       </c>
       <c r="M9" s="26"/>
       <c r="N9" s="26"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3039,8 +3088,11 @@
       </c>
       <c r="M10" s="26"/>
       <c r="N10" s="26"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3070,8 +3122,11 @@
       </c>
       <c r="M11" s="26"/>
       <c r="N11" s="26"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3104,8 +3159,11 @@
       </c>
       <c r="M12" s="26"/>
       <c r="N12" s="26"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3135,8 +3193,11 @@
       </c>
       <c r="M13" s="26"/>
       <c r="N13" s="26"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3166,8 +3227,11 @@
       </c>
       <c r="M14" s="26"/>
       <c r="N14" s="26"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3195,8 +3259,11 @@
       </c>
       <c r="M15" s="26"/>
       <c r="N15" s="26"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -3224,8 +3291,11 @@
       </c>
       <c r="M16" s="26"/>
       <c r="N16" s="26"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -3253,8 +3323,11 @@
       </c>
       <c r="M17" s="26"/>
       <c r="N17" s="26"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3295,8 +3368,11 @@
       <c r="N18" s="26" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3324,8 +3400,11 @@
       </c>
       <c r="M19" s="26"/>
       <c r="N19" s="26"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3353,8 +3432,11 @@
       </c>
       <c r="M20" s="26"/>
       <c r="N20" s="26"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3382,8 +3464,11 @@
       </c>
       <c r="M21" s="26"/>
       <c r="N21" s="26"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3411,8 +3496,11 @@
       </c>
       <c r="M22" s="26"/>
       <c r="N22" s="26"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3443,8 +3531,11 @@
       </c>
       <c r="M23" s="26"/>
       <c r="N23" s="26"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3475,8 +3566,11 @@
       </c>
       <c r="M24" s="26"/>
       <c r="N24" s="26"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3507,8 +3601,11 @@
       </c>
       <c r="M25" s="26"/>
       <c r="N25" s="26"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3541,8 +3638,11 @@
       </c>
       <c r="M26" s="26"/>
       <c r="N26" s="26"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3575,8 +3675,11 @@
       </c>
       <c r="M27" s="26"/>
       <c r="N27" s="26"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3607,8 +3710,11 @@
       </c>
       <c r="M28" s="26"/>
       <c r="N28" s="26"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3639,8 +3745,11 @@
       </c>
       <c r="M29" s="26"/>
       <c r="N29" s="26"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3673,8 +3782,11 @@
       </c>
       <c r="M30" s="26"/>
       <c r="N30" s="26"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3704,8 +3816,11 @@
       </c>
       <c r="M31" s="26"/>
       <c r="N31" s="26"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3733,8 +3848,11 @@
       </c>
       <c r="M32" s="26"/>
       <c r="N32" s="26"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3762,8 +3880,11 @@
       </c>
       <c r="M33" s="26"/>
       <c r="N33" s="26"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3791,8 +3912,11 @@
       </c>
       <c r="M34" s="26"/>
       <c r="N34" s="26"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3822,8 +3946,11 @@
       </c>
       <c r="M35" s="26"/>
       <c r="N35" s="26"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3851,8 +3978,11 @@
       </c>
       <c r="M36" s="26"/>
       <c r="N36" s="26"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3885,8 +4015,11 @@
       </c>
       <c r="M37" s="26"/>
       <c r="N37" s="26"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3916,8 +4049,11 @@
       </c>
       <c r="M38" s="26"/>
       <c r="N38" s="26"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3947,8 +4083,11 @@
       </c>
       <c r="M39" s="26"/>
       <c r="N39" s="26"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3978,8 +4117,11 @@
       </c>
       <c r="M40" s="26"/>
       <c r="N40" s="26"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -4007,8 +4149,11 @@
       </c>
       <c r="M41" s="26"/>
       <c r="N41" s="26"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -4036,8 +4181,11 @@
       </c>
       <c r="M42" s="26"/>
       <c r="N42" s="26"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -4065,8 +4213,11 @@
       </c>
       <c r="M43" s="26"/>
       <c r="N43" s="26"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -4094,8 +4245,11 @@
       </c>
       <c r="M44" s="26"/>
       <c r="N44" s="26"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -4123,8 +4277,11 @@
       </c>
       <c r="M45" s="26"/>
       <c r="N45" s="26"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -4154,8 +4311,11 @@
       </c>
       <c r="M46" s="26"/>
       <c r="N46" s="26"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -4183,8 +4343,11 @@
       </c>
       <c r="M47" s="26"/>
       <c r="N47" s="26"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -4214,8 +4377,11 @@
       </c>
       <c r="M48" s="26"/>
       <c r="N48" s="26"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -4245,8 +4411,11 @@
       </c>
       <c r="M49" s="26"/>
       <c r="N49" s="26"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -4274,8 +4443,11 @@
       </c>
       <c r="M50" s="26"/>
       <c r="N50" s="26"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -4303,8 +4475,11 @@
       </c>
       <c r="M51" s="26"/>
       <c r="N51" s="26"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -4334,8 +4509,11 @@
       </c>
       <c r="M52" s="26"/>
       <c r="N52" s="26"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -4361,8 +4539,11 @@
       </c>
       <c r="M53" s="26"/>
       <c r="N53" s="26"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -4392,8 +4573,11 @@
       </c>
       <c r="M54" s="26"/>
       <c r="N54" s="26"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -4421,8 +4605,11 @@
       </c>
       <c r="M55" s="26"/>
       <c r="N55" s="26"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -4452,8 +4639,11 @@
       </c>
       <c r="M56" s="26"/>
       <c r="N56" s="26"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -4479,8 +4669,11 @@
       </c>
       <c r="M57" s="26"/>
       <c r="N57" s="26"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -4506,8 +4699,11 @@
       </c>
       <c r="M58" s="26"/>
       <c r="N58" s="26"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -4533,8 +4729,11 @@
       </c>
       <c r="M59" s="26"/>
       <c r="N59" s="26"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -4560,8 +4759,11 @@
       </c>
       <c r="M60" s="26"/>
       <c r="N60" s="26"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -4587,8 +4789,11 @@
       </c>
       <c r="M61" s="26"/>
       <c r="N61" s="26"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -4627,8 +4832,11 @@
       </c>
       <c r="M62" s="26"/>
       <c r="N62" s="26"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -4654,8 +4862,11 @@
       </c>
       <c r="M63" s="26"/>
       <c r="N63" s="26"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -4681,8 +4892,11 @@
       </c>
       <c r="M64" s="26"/>
       <c r="N64" s="26"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -4708,8 +4922,11 @@
       </c>
       <c r="M65" s="26"/>
       <c r="N65" s="26"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -4735,8 +4952,11 @@
       </c>
       <c r="M66" s="26"/>
       <c r="N66" s="26"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -4762,8 +4982,11 @@
       </c>
       <c r="M67" s="26"/>
       <c r="N67" s="26"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -4789,8 +5012,11 @@
       </c>
       <c r="M68" s="26"/>
       <c r="N68" s="26"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -4816,8 +5042,11 @@
       </c>
       <c r="M69" s="26"/>
       <c r="N69" s="26"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -4843,8 +5072,11 @@
       </c>
       <c r="M70" s="26"/>
       <c r="N70" s="26"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -4870,8 +5102,11 @@
       </c>
       <c r="M71" s="26"/>
       <c r="N71" s="26"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O71" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -4897,8 +5132,11 @@
       </c>
       <c r="M72" s="26"/>
       <c r="N72" s="26"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -4924,8 +5162,11 @@
       </c>
       <c r="M73" s="26"/>
       <c r="N73" s="26"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O73" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -4951,8 +5192,11 @@
       </c>
       <c r="M74" s="26"/>
       <c r="N74" s="26"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -4978,8 +5222,11 @@
       </c>
       <c r="M75" s="26"/>
       <c r="N75" s="26"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -5005,8 +5252,11 @@
       </c>
       <c r="M76" s="26"/>
       <c r="N76" s="26"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -5032,8 +5282,11 @@
       </c>
       <c r="M77" s="26"/>
       <c r="N77" s="26"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -5059,8 +5312,11 @@
       </c>
       <c r="M78" s="26"/>
       <c r="N78" s="26"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -5086,8 +5342,11 @@
       </c>
       <c r="M79" s="26"/>
       <c r="N79" s="26"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -5113,8 +5372,11 @@
       </c>
       <c r="M80" s="26"/>
       <c r="N80" s="26"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -5140,8 +5402,11 @@
       </c>
       <c r="M81" s="26"/>
       <c r="N81" s="26"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O81" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>1</v>
       </c>
@@ -5180,8 +5445,11 @@
       </c>
       <c r="M82" s="26"/>
       <c r="N82" s="26"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O82" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>2</v>
       </c>
@@ -5206,8 +5474,11 @@
       <c r="L83" s="25"/>
       <c r="M83" s="26"/>
       <c r="N83" s="26"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O83" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>3</v>
       </c>
@@ -5233,8 +5504,11 @@
       </c>
       <c r="M84" s="26"/>
       <c r="N84" s="26"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O84" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>4</v>
       </c>
@@ -5260,8 +5534,11 @@
       </c>
       <c r="M85" s="26"/>
       <c r="N85" s="26"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O85" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>5</v>
       </c>
@@ -5294,8 +5571,11 @@
         <v>666</v>
       </c>
       <c r="N86" s="26"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O86" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>6</v>
       </c>
@@ -5321,8 +5601,11 @@
       </c>
       <c r="M87" s="26"/>
       <c r="N87" s="26"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O87" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>7</v>
       </c>
@@ -5348,8 +5631,11 @@
       </c>
       <c r="M88" s="26"/>
       <c r="N88" s="26"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O88" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>8</v>
       </c>
@@ -5385,8 +5671,11 @@
       </c>
       <c r="M89" s="26"/>
       <c r="N89" s="26"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O89" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>9</v>
       </c>
@@ -5418,8 +5707,11 @@
       </c>
       <c r="M90" s="26"/>
       <c r="N90" s="26"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O90" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>10</v>
       </c>
@@ -5447,8 +5739,11 @@
       </c>
       <c r="M91" s="26"/>
       <c r="N91" s="26"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O91" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>11</v>
       </c>
@@ -5474,8 +5769,11 @@
       </c>
       <c r="M92" s="26"/>
       <c r="N92" s="26"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O92" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>12</v>
       </c>
@@ -5501,8 +5799,11 @@
       </c>
       <c r="M93" s="26"/>
       <c r="N93" s="26"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O93" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>13</v>
       </c>
@@ -5521,8 +5822,11 @@
       <c r="L94" s="25"/>
       <c r="M94" s="26"/>
       <c r="N94" s="26"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O94" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>14</v>
       </c>
@@ -5548,8 +5852,11 @@
       </c>
       <c r="M95" s="26"/>
       <c r="N95" s="26"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O95" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>15</v>
       </c>
@@ -5588,8 +5895,11 @@
       </c>
       <c r="M96" s="26"/>
       <c r="N96" s="26"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O96" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>16</v>
       </c>
@@ -5630,8 +5940,11 @@
         <v>667</v>
       </c>
       <c r="N97" s="26"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O97" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>17</v>
       </c>
@@ -5656,8 +5969,11 @@
       <c r="L98" s="25"/>
       <c r="M98" s="26"/>
       <c r="N98" s="26"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O98" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>18</v>
       </c>
@@ -5688,8 +6004,11 @@
         <v>668</v>
       </c>
       <c r="N99" s="26"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O99" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>19</v>
       </c>
@@ -5715,8 +6034,11 @@
       </c>
       <c r="M100" s="26"/>
       <c r="N100" s="26"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O100" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>20</v>
       </c>
@@ -5752,8 +6074,11 @@
       </c>
       <c r="M101" s="26"/>
       <c r="N101" s="26"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O101" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>21</v>
       </c>
@@ -5789,8 +6114,11 @@
       </c>
       <c r="M102" s="26"/>
       <c r="N102" s="26"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O102" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>22</v>
       </c>
@@ -5816,8 +6144,11 @@
       </c>
       <c r="M103" s="26"/>
       <c r="N103" s="26"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O103" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>23</v>
       </c>
@@ -5843,8 +6174,11 @@
       </c>
       <c r="M104" s="26"/>
       <c r="N104" s="26"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O104" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>24</v>
       </c>
@@ -5870,8 +6204,11 @@
       </c>
       <c r="M105" s="26"/>
       <c r="N105" s="26"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O105" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>25</v>
       </c>
@@ -5907,8 +6244,11 @@
       </c>
       <c r="M106" s="26"/>
       <c r="N106" s="26"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O106" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>26</v>
       </c>
@@ -5934,8 +6274,11 @@
       </c>
       <c r="M107" s="26"/>
       <c r="N107" s="26"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O107" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>27</v>
       </c>
@@ -5961,8 +6304,11 @@
       </c>
       <c r="M108" s="26"/>
       <c r="N108" s="26"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O108" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>28</v>
       </c>
@@ -5988,8 +6334,11 @@
       </c>
       <c r="M109" s="26"/>
       <c r="N109" s="26"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O109" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>29</v>
       </c>
@@ -6015,8 +6364,11 @@
       </c>
       <c r="M110" s="26"/>
       <c r="N110" s="26"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O110" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>30</v>
       </c>
@@ -6053,8 +6405,11 @@
       </c>
       <c r="M111" s="26"/>
       <c r="N111" s="26"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O111" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>31</v>
       </c>
@@ -6095,8 +6450,11 @@
       <c r="N112" s="26" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O112" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>32</v>
       </c>
@@ -6137,8 +6495,11 @@
         <v>670</v>
       </c>
       <c r="N113" s="26"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O113" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>33</v>
       </c>
@@ -6179,8 +6540,11 @@
         <v>671</v>
       </c>
       <c r="N114" s="26"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O114" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>34</v>
       </c>
@@ -6219,8 +6583,11 @@
       </c>
       <c r="M115" s="26"/>
       <c r="N115" s="26"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O115" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>35</v>
       </c>
@@ -6261,8 +6628,11 @@
         <v>672</v>
       </c>
       <c r="N116" s="26"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O116" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>36</v>
       </c>
@@ -6299,8 +6669,11 @@
       <c r="N117" s="26" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O117" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>37</v>
       </c>
@@ -6326,8 +6699,11 @@
       </c>
       <c r="M118" s="26"/>
       <c r="N118" s="26"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O118" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>38</v>
       </c>
@@ -6353,8 +6729,11 @@
       </c>
       <c r="M119" s="26"/>
       <c r="N119" s="26"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O119" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>39</v>
       </c>
@@ -6380,8 +6759,11 @@
       </c>
       <c r="M120" s="26"/>
       <c r="N120" s="26"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O120" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>40</v>
       </c>
@@ -6415,8 +6797,11 @@
       </c>
       <c r="M121" s="26"/>
       <c r="N121" s="26"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O121" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>41</v>
       </c>
@@ -6442,8 +6827,11 @@
       </c>
       <c r="M122" s="26"/>
       <c r="N122" s="26"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O122" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>42</v>
       </c>
@@ -6469,8 +6857,11 @@
       </c>
       <c r="M123" s="26"/>
       <c r="N123" s="26"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O123" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>43</v>
       </c>
@@ -6509,8 +6900,11 @@
       </c>
       <c r="M124" s="26"/>
       <c r="N124" s="26"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O124" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>44</v>
       </c>
@@ -6536,8 +6930,11 @@
       </c>
       <c r="M125" s="26"/>
       <c r="N125" s="26"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O125" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>45</v>
       </c>
@@ -6563,8 +6960,11 @@
       </c>
       <c r="M126" s="26"/>
       <c r="N126" s="26"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O126" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>46</v>
       </c>
@@ -6597,8 +6997,11 @@
       </c>
       <c r="M127" s="26"/>
       <c r="N127" s="26"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O127" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>47</v>
       </c>
@@ -6634,8 +7037,11 @@
       </c>
       <c r="M128" s="26"/>
       <c r="N128" s="26"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O128" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>48</v>
       </c>
@@ -6660,8 +7066,11 @@
       <c r="L129" s="25"/>
       <c r="M129" s="26"/>
       <c r="N129" s="26"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O129" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>49</v>
       </c>
@@ -6700,8 +7109,11 @@
       </c>
       <c r="M130" s="26"/>
       <c r="N130" s="26"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O130" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>50</v>
       </c>
@@ -6731,8 +7143,11 @@
       </c>
       <c r="M131" s="26"/>
       <c r="N131" s="26"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O131" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>51</v>
       </c>
@@ -6758,8 +7173,11 @@
       </c>
       <c r="M132" s="26"/>
       <c r="N132" s="26"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O132" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>52</v>
       </c>
@@ -6795,8 +7213,11 @@
       </c>
       <c r="M133" s="26"/>
       <c r="N133" s="26"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O133" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>53</v>
       </c>
@@ -6822,8 +7243,11 @@
       </c>
       <c r="M134" s="26"/>
       <c r="N134" s="26"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O134" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>54</v>
       </c>
@@ -6859,8 +7283,11 @@
       </c>
       <c r="M135" s="26"/>
       <c r="N135" s="26"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O135" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>55</v>
       </c>
@@ -6896,8 +7323,11 @@
       </c>
       <c r="M136" s="26"/>
       <c r="N136" s="26"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O136" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>56</v>
       </c>
@@ -6923,8 +7353,11 @@
       </c>
       <c r="M137" s="26"/>
       <c r="N137" s="26"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O137" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>57</v>
       </c>
@@ -6960,8 +7393,11 @@
       </c>
       <c r="M138" s="26"/>
       <c r="N138" s="26"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O138" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>58</v>
       </c>
@@ -7000,8 +7436,11 @@
       </c>
       <c r="M139" s="26"/>
       <c r="N139" s="26"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O139" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>59</v>
       </c>
@@ -7029,8 +7468,11 @@
       </c>
       <c r="M140" s="26"/>
       <c r="N140" s="26"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O140" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>60</v>
       </c>
@@ -7055,8 +7497,11 @@
       <c r="L141" s="25"/>
       <c r="M141" s="26"/>
       <c r="N141" s="26"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O141" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>61</v>
       </c>
@@ -7080,8 +7525,11 @@
       </c>
       <c r="M142" s="26"/>
       <c r="N142" s="26"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O142" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>62</v>
       </c>
@@ -7122,8 +7570,11 @@
         <v>675</v>
       </c>
       <c r="N143" s="26"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O143" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>63</v>
       </c>
@@ -7162,8 +7613,11 @@
       </c>
       <c r="M144" s="26"/>
       <c r="N144" s="26"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O144" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>64</v>
       </c>
@@ -7188,8 +7642,11 @@
       <c r="L145" s="25"/>
       <c r="M145" s="26"/>
       <c r="N145" s="26"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O145" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>65</v>
       </c>
@@ -7217,8 +7674,11 @@
       </c>
       <c r="M146" s="26"/>
       <c r="N146" s="26"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O146" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>66</v>
       </c>
@@ -7251,8 +7711,11 @@
       </c>
       <c r="M147" s="26"/>
       <c r="N147" s="26"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O147" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>67</v>
       </c>
@@ -7278,8 +7741,11 @@
       </c>
       <c r="M148" s="26"/>
       <c r="N148" s="26"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O148" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>68</v>
       </c>
@@ -7305,8 +7771,11 @@
       </c>
       <c r="M149" s="26"/>
       <c r="N149" s="26"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O149" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>69</v>
       </c>
@@ -7332,8 +7801,11 @@
       </c>
       <c r="M150" s="26"/>
       <c r="N150" s="26"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O150" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>70</v>
       </c>
@@ -7369,8 +7841,11 @@
       </c>
       <c r="M151" s="26"/>
       <c r="N151" s="26"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O151" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>71</v>
       </c>
@@ -7396,8 +7871,11 @@
       </c>
       <c r="M152" s="26"/>
       <c r="N152" s="26"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O152" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>72</v>
       </c>
@@ -7431,8 +7909,11 @@
       </c>
       <c r="M153" s="26"/>
       <c r="N153" s="26"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O153" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>73</v>
       </c>
@@ -7471,8 +7952,11 @@
       </c>
       <c r="M154" s="26"/>
       <c r="N154" s="26"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O154" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>74</v>
       </c>
@@ -7504,8 +7988,11 @@
       </c>
       <c r="M155" s="26"/>
       <c r="N155" s="26"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O155" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>75</v>
       </c>
@@ -7529,8 +8016,11 @@
       </c>
       <c r="M156" s="26"/>
       <c r="N156" s="26"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O156" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>76</v>
       </c>
@@ -7555,8 +8045,11 @@
       <c r="L157" s="25"/>
       <c r="M157" s="26"/>
       <c r="N157" s="26"/>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O157" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>77</v>
       </c>
@@ -7595,8 +8088,11 @@
       </c>
       <c r="M158" s="26"/>
       <c r="N158" s="26"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O158" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>78</v>
       </c>
@@ -7620,8 +8116,11 @@
       </c>
       <c r="M159" s="26"/>
       <c r="N159" s="26"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O159" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>79</v>
       </c>
@@ -7645,8 +8144,11 @@
       </c>
       <c r="M160" s="26"/>
       <c r="N160" s="26"/>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O160" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>80</v>
       </c>
@@ -7682,8 +8184,11 @@
       </c>
       <c r="M161" s="26"/>
       <c r="N161" s="26"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O161" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>81</v>
       </c>
@@ -7722,8 +8227,11 @@
       </c>
       <c r="M162" s="26"/>
       <c r="N162" s="26"/>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O162" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>82</v>
       </c>
@@ -7749,8 +8257,11 @@
       </c>
       <c r="M163" s="26"/>
       <c r="N163" s="26"/>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O163" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>83</v>
       </c>
@@ -7776,8 +8287,11 @@
       </c>
       <c r="M164" s="26"/>
       <c r="N164" s="26"/>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O164" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>84</v>
       </c>
@@ -7803,8 +8317,11 @@
       </c>
       <c r="M165" s="26"/>
       <c r="N165" s="26"/>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O165" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>85</v>
       </c>
@@ -7830,8 +8347,11 @@
       </c>
       <c r="M166" s="26"/>
       <c r="N166" s="26"/>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O166" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>86</v>
       </c>
@@ -7857,8 +8377,11 @@
       </c>
       <c r="M167" s="26"/>
       <c r="N167" s="26"/>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O167" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>87</v>
       </c>
@@ -7894,8 +8417,11 @@
       </c>
       <c r="M168" s="26"/>
       <c r="N168" s="26"/>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O168" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>88</v>
       </c>
@@ -7919,8 +8445,11 @@
       </c>
       <c r="M169" s="26"/>
       <c r="N169" s="26"/>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O169" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>89</v>
       </c>
@@ -7956,8 +8485,11 @@
       </c>
       <c r="M170" s="26"/>
       <c r="N170" s="26"/>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O170" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>90</v>
       </c>
@@ -7981,8 +8513,11 @@
       </c>
       <c r="M171" s="26"/>
       <c r="N171" s="26"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O171" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>91</v>
       </c>
@@ -8006,8 +8541,11 @@
       </c>
       <c r="M172" s="26"/>
       <c r="N172" s="26"/>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O172" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>92</v>
       </c>
@@ -8031,8 +8569,11 @@
       </c>
       <c r="M173" s="26"/>
       <c r="N173" s="26"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O173" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>93</v>
       </c>
@@ -8056,8 +8597,11 @@
       </c>
       <c r="M174" s="26"/>
       <c r="N174" s="26"/>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O174" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>94</v>
       </c>
@@ -8081,8 +8625,11 @@
       </c>
       <c r="M175" s="26"/>
       <c r="N175" s="26"/>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O175" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>95</v>
       </c>
@@ -8116,8 +8663,11 @@
       </c>
       <c r="M176" s="26"/>
       <c r="N176" s="26"/>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O176" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>96</v>
       </c>
@@ -8142,8 +8692,11 @@
       <c r="L177" s="25"/>
       <c r="M177" s="26"/>
       <c r="N177" s="26"/>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O177" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>97</v>
       </c>
@@ -8179,8 +8732,11 @@
       </c>
       <c r="M178" s="26"/>
       <c r="N178" s="26"/>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O178" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>98</v>
       </c>
@@ -8206,8 +8762,11 @@
       </c>
       <c r="M179" s="26"/>
       <c r="N179" s="26"/>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O179" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>99</v>
       </c>
@@ -8233,8 +8792,11 @@
       </c>
       <c r="M180" s="26"/>
       <c r="N180" s="26"/>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O180" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>100</v>
       </c>
@@ -8264,8 +8826,11 @@
       </c>
       <c r="M181" s="26"/>
       <c r="N181" s="26"/>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O181" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>101</v>
       </c>
@@ -8291,8 +8856,11 @@
       </c>
       <c r="M182" s="26"/>
       <c r="N182" s="26"/>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O182" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>102</v>
       </c>
@@ -8318,8 +8886,11 @@
       </c>
       <c r="M183" s="26"/>
       <c r="N183" s="26"/>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O183" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>103</v>
       </c>
@@ -8343,8 +8914,11 @@
       </c>
       <c r="M184" s="26"/>
       <c r="N184" s="26"/>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O184" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>104</v>
       </c>
@@ -8383,8 +8957,11 @@
       </c>
       <c r="M185" s="26"/>
       <c r="N185" s="26"/>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O185" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>105</v>
       </c>
@@ -8408,8 +8985,11 @@
       </c>
       <c r="M186" s="26"/>
       <c r="N186" s="26"/>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O186" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>106</v>
       </c>
@@ -8434,8 +9014,11 @@
       <c r="L187" s="25"/>
       <c r="M187" s="26"/>
       <c r="N187" s="26"/>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O187" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>107</v>
       </c>
@@ -8460,8 +9043,11 @@
       <c r="L188" s="25"/>
       <c r="M188" s="26"/>
       <c r="N188" s="26"/>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O188" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>108</v>
       </c>
@@ -8485,8 +9071,11 @@
       </c>
       <c r="M189" s="26"/>
       <c r="N189" s="26"/>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O189" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>109</v>
       </c>
@@ -8510,8 +9099,11 @@
       </c>
       <c r="M190" s="26"/>
       <c r="N190" s="26"/>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O190" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>110</v>
       </c>
@@ -8544,8 +9136,11 @@
         <v>676</v>
       </c>
       <c r="N191" s="26"/>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O191" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>111</v>
       </c>
@@ -8570,8 +9165,11 @@
       <c r="L192" s="25"/>
       <c r="M192" s="26"/>
       <c r="N192" s="26"/>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O192" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>112</v>
       </c>
@@ -8601,8 +9199,11 @@
       </c>
       <c r="M193" s="26"/>
       <c r="N193" s="26"/>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O193" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>113</v>
       </c>
@@ -8633,8 +9234,11 @@
         <v>677</v>
       </c>
       <c r="N194" s="26"/>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O194" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>114</v>
       </c>
@@ -8673,8 +9277,11 @@
       </c>
       <c r="M195" s="26"/>
       <c r="N195" s="26"/>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O195" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>115</v>
       </c>
@@ -8715,8 +9322,11 @@
       <c r="N196" s="26" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O196" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>116</v>
       </c>
@@ -8742,8 +9352,11 @@
       </c>
       <c r="M197" s="26"/>
       <c r="N197" s="26"/>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O197" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>117</v>
       </c>
@@ -8782,8 +9395,11 @@
       </c>
       <c r="M198" s="26"/>
       <c r="N198" s="26"/>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O198" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>118</v>
       </c>
@@ -8807,8 +9423,11 @@
       </c>
       <c r="M199" s="26"/>
       <c r="N199" s="26"/>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O199" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>119</v>
       </c>
@@ -8833,8 +9452,11 @@
       <c r="L200" s="25"/>
       <c r="M200" s="26"/>
       <c r="N200" s="26"/>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O200" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>120</v>
       </c>
@@ -8858,8 +9480,11 @@
       </c>
       <c r="M201" s="26"/>
       <c r="N201" s="26"/>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O201" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>1</v>
       </c>
@@ -8898,8 +9523,11 @@
       </c>
       <c r="M202" s="26"/>
       <c r="N202" s="26"/>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O202" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
         <v>2</v>
       </c>
@@ -8938,8 +9566,11 @@
       </c>
       <c r="M203" s="26"/>
       <c r="N203" s="26"/>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O203" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
         <v>3</v>
       </c>
@@ -8972,8 +9603,11 @@
         <v>679</v>
       </c>
       <c r="N204" s="26"/>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O204" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>4</v>
       </c>
@@ -9012,8 +9646,11 @@
       </c>
       <c r="M205" s="26"/>
       <c r="N205" s="26"/>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O205" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
         <v>5</v>
       </c>
@@ -9049,8 +9686,11 @@
       </c>
       <c r="M206" s="26"/>
       <c r="N206" s="26"/>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O206" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>6</v>
       </c>
@@ -9091,8 +9731,11 @@
       <c r="N207" s="26" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O207" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" s="5">
         <v>7</v>
       </c>
@@ -9127,8 +9770,11 @@
       </c>
       <c r="M208" s="26"/>
       <c r="N208" s="26"/>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O208" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
         <v>8</v>
       </c>
@@ -9155,8 +9801,11 @@
       </c>
       <c r="M209" s="26"/>
       <c r="N209" s="26"/>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O209" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>9</v>
       </c>
@@ -9195,8 +9844,11 @@
       </c>
       <c r="M210" s="26"/>
       <c r="N210" s="26"/>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O210" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>10</v>
       </c>
@@ -9232,8 +9884,11 @@
       </c>
       <c r="M211" s="26"/>
       <c r="N211" s="26"/>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O211" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
         <v>11</v>
       </c>
@@ -9272,8 +9927,11 @@
       </c>
       <c r="M212" s="26"/>
       <c r="N212" s="26"/>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O212" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>12</v>
       </c>
@@ -9312,8 +9970,11 @@
       </c>
       <c r="M213" s="26"/>
       <c r="N213" s="26"/>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O213" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>13</v>
       </c>
@@ -9349,8 +10010,11 @@
       </c>
       <c r="M214" s="26"/>
       <c r="N214" s="26"/>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O214" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
         <v>14</v>
       </c>
@@ -9384,8 +10048,11 @@
       </c>
       <c r="M215" s="26"/>
       <c r="N215" s="26"/>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O215" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>15</v>
       </c>
@@ -9421,8 +10088,11 @@
       </c>
       <c r="M216" s="26"/>
       <c r="N216" s="26"/>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O216" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>16</v>
       </c>
@@ -9461,8 +10131,11 @@
       </c>
       <c r="M217" s="26"/>
       <c r="N217" s="26"/>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O217" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
         <v>17</v>
       </c>
@@ -9493,8 +10166,11 @@
         <v>677</v>
       </c>
       <c r="N218" s="26"/>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O218" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>18</v>
       </c>
@@ -9535,8 +10211,11 @@
       <c r="N219" s="26" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O219" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" s="7">
         <v>19</v>
       </c>
@@ -9572,8 +10251,11 @@
       </c>
       <c r="M220" s="26"/>
       <c r="N220" s="26"/>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O220" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>20</v>
       </c>
@@ -9614,6 +10296,9 @@
         <v>682</v>
       </c>
       <c r="N221" s="26"/>
+      <c r="O221" s="5">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C221">

--- a/booking.xlsx
+++ b/booking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ATS\crm_house\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EF0390B-A2B5-4D60-9D2C-9360EA730D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474A8B54-E7DD-418C-AE0D-ADC0953DACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D9B1116C-A23B-4F7B-8FBF-BBA33CFC25B0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="700">
   <si>
     <t>Sotildi</t>
   </si>
@@ -2129,12 +2129,22 @@
   </si>
   <si>
     <t>Bino</t>
+  </si>
+  <si>
+    <t>Pasport berilgan sana</t>
+  </si>
+  <si>
+    <t>23.062022</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="165" formatCode="d\.m\.yyyy"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2318,7 +2328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2391,6 +2401,30 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2739,7 +2773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E987B6-1276-4D84-83C3-2F672E3C8C43}">
-  <dimension ref="A1:O221"/>
+  <dimension ref="A1:P221"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" customWidth="1"/>
@@ -2756,9 +2790,10 @@
     <col min="13" max="13" width="10.21875" customWidth="1"/>
     <col min="14" max="14" width="10.44140625" customWidth="1"/>
     <col min="15" max="15" width="8.109375" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="10" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>683</v>
       </c>
@@ -2804,8 +2839,11 @@
       <c r="O1" s="28" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="28" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2838,8 +2876,9 @@
       <c r="O2" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2" s="29"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2868,8 +2907,9 @@
       <c r="O3" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3" s="29"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2898,8 +2938,9 @@
       <c r="O4" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4" s="29"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2928,8 +2969,9 @@
       <c r="O5" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5" s="29"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2962,8 +3004,9 @@
       <c r="O6" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6" s="29"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2994,8 +3037,9 @@
       <c r="O7" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" s="29"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3026,8 +3070,9 @@
       <c r="O8" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" s="29"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3061,8 +3106,9 @@
       <c r="O9" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" s="29"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3091,8 +3137,9 @@
       <c r="O10" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" s="29"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3125,8 +3172,9 @@
       <c r="O11" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11" s="29"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3162,8 +3210,9 @@
       <c r="O12" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12" s="29"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3196,8 +3245,9 @@
       <c r="O13" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13" s="29"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3230,8 +3280,9 @@
       <c r="O14" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14" s="29"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3262,8 +3313,9 @@
       <c r="O15" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" s="29"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -3294,8 +3346,9 @@
       <c r="O16" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16" s="29"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -3326,8 +3379,9 @@
       <c r="O17" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17" s="29"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3371,8 +3425,11 @@
       <c r="O18" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3403,8 +3460,9 @@
       <c r="O19" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P19" s="29"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3435,8 +3493,9 @@
       <c r="O20" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P20" s="29"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3467,8 +3526,9 @@
       <c r="O21" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P21" s="29"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3499,8 +3559,9 @@
       <c r="O22" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P22" s="29"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3534,8 +3595,9 @@
       <c r="O23" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P23" s="29"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3569,8 +3631,9 @@
       <c r="O24" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P24" s="29"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3604,8 +3667,9 @@
       <c r="O25" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P25" s="29"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3641,8 +3705,9 @@
       <c r="O26" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P26" s="29"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3678,8 +3743,9 @@
       <c r="O27" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P27" s="29"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3713,8 +3779,9 @@
       <c r="O28" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P28" s="29"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3748,8 +3815,9 @@
       <c r="O29" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P29" s="29"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3785,8 +3853,9 @@
       <c r="O30" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P30" s="29"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3819,8 +3888,9 @@
       <c r="O31" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P31" s="29"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3851,8 +3921,9 @@
       <c r="O32" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P32" s="29"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3883,8 +3954,9 @@
       <c r="O33" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P33" s="29"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3915,8 +3987,9 @@
       <c r="O34" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P34" s="29"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3949,8 +4022,9 @@
       <c r="O35" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P35" s="29"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3981,8 +4055,9 @@
       <c r="O36" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P36" s="29"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -4018,8 +4093,9 @@
       <c r="O37" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P37" s="29"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -4052,8 +4128,9 @@
       <c r="O38" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P38" s="29"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -4086,8 +4163,9 @@
       <c r="O39" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P39" s="29"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -4120,8 +4198,9 @@
       <c r="O40" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P40" s="29"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -4152,8 +4231,9 @@
       <c r="O41" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P41" s="29"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -4184,8 +4264,9 @@
       <c r="O42" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P42" s="29"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -4216,8 +4297,9 @@
       <c r="O43" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P43" s="29"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -4248,8 +4330,9 @@
       <c r="O44" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P44" s="29"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -4280,8 +4363,9 @@
       <c r="O45" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P45" s="29"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -4314,8 +4398,9 @@
       <c r="O46" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P46" s="29"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -4346,8 +4431,9 @@
       <c r="O47" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P47" s="29"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -4380,8 +4466,9 @@
       <c r="O48" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P48" s="29"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -4414,8 +4501,9 @@
       <c r="O49" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P49" s="29"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -4446,8 +4534,9 @@
       <c r="O50" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P50" s="29"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -4478,8 +4567,9 @@
       <c r="O51" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P51" s="29"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -4512,8 +4602,9 @@
       <c r="O52" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P52" s="29"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -4542,8 +4633,9 @@
       <c r="O53" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P53" s="29"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -4576,8 +4668,9 @@
       <c r="O54" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P54" s="29"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -4608,8 +4701,9 @@
       <c r="O55" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P55" s="29"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -4642,8 +4736,9 @@
       <c r="O56" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P56" s="29"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -4672,8 +4767,9 @@
       <c r="O57" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P57" s="29"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -4702,8 +4798,9 @@
       <c r="O58" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P58" s="29"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -4732,8 +4829,9 @@
       <c r="O59" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P59" s="29"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -4762,8 +4860,9 @@
       <c r="O60" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P60" s="29"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -4792,8 +4891,9 @@
       <c r="O61" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P61" s="29"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -4835,8 +4935,11 @@
       <c r="O62" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P62" s="29">
+        <v>45579</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -4865,8 +4968,9 @@
       <c r="O63" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P63" s="29"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -4895,8 +4999,9 @@
       <c r="O64" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P64" s="29"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -4925,8 +5030,9 @@
       <c r="O65" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P65" s="29"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -4955,8 +5061,9 @@
       <c r="O66" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P66" s="29"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -4985,8 +5092,9 @@
       <c r="O67" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P67" s="29"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -5015,8 +5123,9 @@
       <c r="O68" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P68" s="29"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -5045,8 +5154,9 @@
       <c r="O69" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P69" s="29"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -5075,8 +5185,9 @@
       <c r="O70" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P70" s="29"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -5105,8 +5216,9 @@
       <c r="O71" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P71" s="29"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -5135,8 +5247,9 @@
       <c r="O72" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P72" s="29"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -5165,8 +5278,9 @@
       <c r="O73" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P73" s="29"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -5195,8 +5309,9 @@
       <c r="O74" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P74" s="29"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -5225,8 +5340,9 @@
       <c r="O75" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P75" s="29"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -5255,8 +5371,9 @@
       <c r="O76" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P76" s="29"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -5285,8 +5402,9 @@
       <c r="O77" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P77" s="29"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -5315,8 +5433,9 @@
       <c r="O78" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P78" s="29"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -5345,8 +5464,9 @@
       <c r="O79" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P79" s="29"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -5375,8 +5495,9 @@
       <c r="O80" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P80" s="29"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -5405,8 +5526,9 @@
       <c r="O81" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P81" s="30"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>1</v>
       </c>
@@ -5448,8 +5570,11 @@
       <c r="O82" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P82" s="31">
+        <v>43211</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>2</v>
       </c>
@@ -5477,8 +5602,9 @@
       <c r="O83" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P83" s="32"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>3</v>
       </c>
@@ -5507,8 +5633,9 @@
       <c r="O84" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P84" s="31"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>4</v>
       </c>
@@ -5537,8 +5664,9 @@
       <c r="O85" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P85" s="32"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>5</v>
       </c>
@@ -5574,8 +5702,9 @@
       <c r="O86" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P86" s="31"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>6</v>
       </c>
@@ -5604,8 +5733,9 @@
       <c r="O87" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P87" s="32"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>7</v>
       </c>
@@ -5634,8 +5764,9 @@
       <c r="O88" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P88" s="31"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>8</v>
       </c>
@@ -5674,8 +5805,11 @@
       <c r="O89" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P89" s="32">
+        <v>42924</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>9</v>
       </c>
@@ -5710,8 +5844,11 @@
       <c r="O90" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P90" s="31">
+        <v>43097</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>10</v>
       </c>
@@ -5742,8 +5879,9 @@
       <c r="O91" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P91" s="4"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>11</v>
       </c>
@@ -5772,8 +5910,9 @@
       <c r="O92" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P92" s="31"/>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>12</v>
       </c>
@@ -5802,8 +5941,9 @@
       <c r="O93" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P93" s="32"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>13</v>
       </c>
@@ -5825,8 +5965,9 @@
       <c r="O94" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>14</v>
       </c>
@@ -5855,8 +5996,9 @@
       <c r="O95" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P95" s="32"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>15</v>
       </c>
@@ -5898,8 +6040,11 @@
       <c r="O96" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P96" s="3" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>16</v>
       </c>
@@ -5943,8 +6088,11 @@
       <c r="O97" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P97" s="32">
+        <v>46016</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>17</v>
       </c>
@@ -5972,8 +6120,9 @@
       <c r="O98" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P98" s="31"/>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>18</v>
       </c>
@@ -6007,8 +6156,9 @@
       <c r="O99" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P99" s="32"/>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>19</v>
       </c>
@@ -6037,8 +6187,9 @@
       <c r="O100" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P100" s="31"/>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>20</v>
       </c>
@@ -6077,8 +6228,11 @@
       <c r="O101" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P101" s="31">
+        <v>45069</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>21</v>
       </c>
@@ -6117,8 +6271,11 @@
       <c r="O102" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P102" s="31">
+        <v>42618</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>22</v>
       </c>
@@ -6147,8 +6304,9 @@
       <c r="O103" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P103" s="32"/>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>23</v>
       </c>
@@ -6177,8 +6335,9 @@
       <c r="O104" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P104" s="31"/>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>24</v>
       </c>
@@ -6207,8 +6366,9 @@
       <c r="O105" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P105" s="32"/>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>25</v>
       </c>
@@ -6247,8 +6407,11 @@
       <c r="O106" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P106" s="31">
+        <v>45797</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>26</v>
       </c>
@@ -6277,8 +6440,9 @@
       <c r="O107" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P107" s="32"/>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>27</v>
       </c>
@@ -6307,8 +6471,9 @@
       <c r="O108" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P108" s="31"/>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>28</v>
       </c>
@@ -6337,8 +6502,9 @@
       <c r="O109" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P109" s="32"/>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>29</v>
       </c>
@@ -6367,8 +6533,9 @@
       <c r="O110" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P110" s="31"/>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>30</v>
       </c>
@@ -6408,8 +6575,11 @@
       <c r="O111" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P111" s="32">
+        <v>43197</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>31</v>
       </c>
@@ -6453,8 +6623,11 @@
       <c r="O112" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P112" s="31">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>32</v>
       </c>
@@ -6498,8 +6671,11 @@
       <c r="O113" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P113" s="32">
+        <v>42929</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>33</v>
       </c>
@@ -6543,8 +6719,11 @@
       <c r="O114" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P114" s="31">
+        <v>37765</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>34</v>
       </c>
@@ -6586,8 +6765,11 @@
       <c r="O115" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P115" s="32">
+        <v>45191</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>35</v>
       </c>
@@ -6631,8 +6813,11 @@
       <c r="O116" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P116" s="31">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>36</v>
       </c>
@@ -6672,8 +6857,9 @@
       <c r="O117" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P117" s="32"/>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>37</v>
       </c>
@@ -6702,8 +6888,9 @@
       <c r="O118" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P118" s="31"/>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>38</v>
       </c>
@@ -6732,8 +6919,9 @@
       <c r="O119" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P119" s="32"/>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>39</v>
       </c>
@@ -6762,8 +6950,9 @@
       <c r="O120" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P120" s="31"/>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>40</v>
       </c>
@@ -6800,8 +6989,11 @@
       <c r="O121" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P121" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>41</v>
       </c>
@@ -6830,8 +7022,9 @@
       <c r="O122" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P122" s="31"/>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>42</v>
       </c>
@@ -6860,8 +7053,9 @@
       <c r="O123" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P123" s="32"/>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>43</v>
       </c>
@@ -6903,8 +7097,11 @@
       <c r="O124" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P124" s="31">
+        <v>44922</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>44</v>
       </c>
@@ -6933,8 +7130,9 @@
       <c r="O125" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P125" s="32"/>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>45</v>
       </c>
@@ -6963,8 +7161,9 @@
       <c r="O126" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P126" s="31"/>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>46</v>
       </c>
@@ -7000,8 +7199,9 @@
       <c r="O127" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P127" s="32"/>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>47</v>
       </c>
@@ -7040,8 +7240,11 @@
       <c r="O128" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P128" s="31">
+        <v>42511</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>48</v>
       </c>
@@ -7069,8 +7272,9 @@
       <c r="O129" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P129" s="32"/>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>49</v>
       </c>
@@ -7112,8 +7316,11 @@
       <c r="O130" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P130" s="33">
+        <v>43815</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>50</v>
       </c>
@@ -7146,8 +7353,9 @@
       <c r="O131" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P131" s="32"/>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>51</v>
       </c>
@@ -7176,8 +7384,9 @@
       <c r="O132" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P132" s="31"/>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>52</v>
       </c>
@@ -7216,8 +7425,11 @@
       <c r="O133" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P133" s="32">
+        <v>45128</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>53</v>
       </c>
@@ -7246,8 +7458,9 @@
       <c r="O134" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P134" s="31"/>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>54</v>
       </c>
@@ -7286,8 +7499,11 @@
       <c r="O135" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P135" s="32">
+        <v>42888</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>55</v>
       </c>
@@ -7326,8 +7542,11 @@
       <c r="O136" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P136" s="31">
+        <v>42969</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>56</v>
       </c>
@@ -7356,8 +7575,9 @@
       <c r="O137" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P137" s="32"/>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>57</v>
       </c>
@@ -7396,8 +7616,11 @@
       <c r="O138" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P138" s="31">
+        <v>42954</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>58</v>
       </c>
@@ -7439,8 +7662,11 @@
       <c r="O139" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P139" s="32">
+        <v>46067</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>59</v>
       </c>
@@ -7471,8 +7697,9 @@
       <c r="O140" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P140" s="31"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>60</v>
       </c>
@@ -7500,8 +7727,9 @@
       <c r="O141" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P141" s="32"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>61</v>
       </c>
@@ -7528,8 +7756,9 @@
       <c r="O142" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P142" s="31"/>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>62</v>
       </c>
@@ -7573,8 +7802,11 @@
       <c r="O143" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P143" s="32">
+        <v>45534</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>63</v>
       </c>
@@ -7616,8 +7848,11 @@
       <c r="O144" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P144" s="31">
+        <v>43372</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>64</v>
       </c>
@@ -7645,8 +7880,9 @@
       <c r="O145" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P145" s="32"/>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>65</v>
       </c>
@@ -7677,8 +7913,9 @@
       <c r="O146" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P146" s="31"/>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>66</v>
       </c>
@@ -7714,8 +7951,9 @@
       <c r="O147" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P147" s="32"/>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>67</v>
       </c>
@@ -7744,8 +7982,9 @@
       <c r="O148" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P148" s="33"/>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>68</v>
       </c>
@@ -7774,8 +8013,9 @@
       <c r="O149" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P149" s="32"/>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>69</v>
       </c>
@@ -7804,8 +8044,9 @@
       <c r="O150" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P150" s="31"/>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>70</v>
       </c>
@@ -7844,8 +8085,11 @@
       <c r="O151" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P151" s="32">
+        <v>43264</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>71</v>
       </c>
@@ -7874,8 +8118,9 @@
       <c r="O152" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P152" s="31"/>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>72</v>
       </c>
@@ -7912,8 +8157,11 @@
       <c r="O153" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P153" s="32">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>73</v>
       </c>
@@ -7955,8 +8203,11 @@
       <c r="O154" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P154" s="31">
+        <v>43318</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>74</v>
       </c>
@@ -7991,8 +8242,9 @@
       <c r="O155" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P155" s="32"/>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>75</v>
       </c>
@@ -8019,8 +8271,9 @@
       <c r="O156" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P156" s="31"/>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>76</v>
       </c>
@@ -8048,8 +8301,9 @@
       <c r="O157" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P157" s="32"/>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>77</v>
       </c>
@@ -8091,8 +8345,11 @@
       <c r="O158" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P158" s="31">
+        <v>45812</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>78</v>
       </c>
@@ -8119,8 +8376,9 @@
       <c r="O159" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P159" s="32"/>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>79</v>
       </c>
@@ -8147,8 +8405,9 @@
       <c r="O160" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P160" s="31"/>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>80</v>
       </c>
@@ -8187,8 +8446,11 @@
       <c r="O161" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P161" s="32">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>81</v>
       </c>
@@ -8230,8 +8492,11 @@
       <c r="O162" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P162" s="31">
+        <v>45189</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>82</v>
       </c>
@@ -8260,8 +8525,9 @@
       <c r="O163" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P163" s="32"/>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>83</v>
       </c>
@@ -8290,8 +8556,9 @@
       <c r="O164" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P164" s="31"/>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>84</v>
       </c>
@@ -8320,8 +8587,9 @@
       <c r="O165" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P165" s="32"/>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>85</v>
       </c>
@@ -8350,8 +8618,9 @@
       <c r="O166" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P166" s="31"/>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>86</v>
       </c>
@@ -8380,8 +8649,9 @@
       <c r="O167" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P167" s="32"/>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>87</v>
       </c>
@@ -8420,8 +8690,11 @@
       <c r="O168" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P168" s="31">
+        <v>42716</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>88</v>
       </c>
@@ -8448,8 +8721,9 @@
       <c r="O169" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P169" s="32"/>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>89</v>
       </c>
@@ -8488,8 +8762,11 @@
       <c r="O170" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P170" s="31">
+        <v>42514</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>90</v>
       </c>
@@ -8516,8 +8793,9 @@
       <c r="O171" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P171" s="32"/>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>91</v>
       </c>
@@ -8544,8 +8822,9 @@
       <c r="O172" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P172" s="31"/>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>92</v>
       </c>
@@ -8572,8 +8851,9 @@
       <c r="O173" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P173" s="32"/>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>93</v>
       </c>
@@ -8600,8 +8880,9 @@
       <c r="O174" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P174" s="31"/>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>94</v>
       </c>
@@ -8628,8 +8909,9 @@
       <c r="O175" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P175" s="32"/>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>95</v>
       </c>
@@ -8666,8 +8948,11 @@
       <c r="O176" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P176" s="31">
+        <v>42770</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>96</v>
       </c>
@@ -8695,8 +8980,9 @@
       <c r="O177" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P177" s="32"/>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>97</v>
       </c>
@@ -8735,8 +9021,11 @@
       <c r="O178" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P178" s="31">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>98</v>
       </c>
@@ -8765,8 +9054,9 @@
       <c r="O179" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P179" s="32"/>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>99</v>
       </c>
@@ -8795,8 +9085,9 @@
       <c r="O180" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P180" s="31"/>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>100</v>
       </c>
@@ -8829,8 +9120,9 @@
       <c r="O181" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P181" s="32"/>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>101</v>
       </c>
@@ -8859,8 +9151,9 @@
       <c r="O182" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P182" s="31"/>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>102</v>
       </c>
@@ -8889,8 +9182,9 @@
       <c r="O183" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P183" s="32"/>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>103</v>
       </c>
@@ -8917,8 +9211,9 @@
       <c r="O184" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P184" s="31"/>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>104</v>
       </c>
@@ -8960,8 +9255,11 @@
       <c r="O185" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P185" s="32">
+        <v>44575</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>105</v>
       </c>
@@ -8988,8 +9286,9 @@
       <c r="O186" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P186" s="31"/>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>106</v>
       </c>
@@ -9017,8 +9316,9 @@
       <c r="O187" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P187" s="32"/>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>107</v>
       </c>
@@ -9046,8 +9346,9 @@
       <c r="O188" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P188" s="31"/>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>108</v>
       </c>
@@ -9074,8 +9375,9 @@
       <c r="O189" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P189" s="32"/>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>109</v>
       </c>
@@ -9102,8 +9404,9 @@
       <c r="O190" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P190" s="31"/>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>110</v>
       </c>
@@ -9139,8 +9442,9 @@
       <c r="O191" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P191" s="4"/>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>111</v>
       </c>
@@ -9168,8 +9472,9 @@
       <c r="O192" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P192" s="31"/>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>112</v>
       </c>
@@ -9202,8 +9507,9 @@
       <c r="O193" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P193" s="32"/>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>113</v>
       </c>
@@ -9237,8 +9543,9 @@
       <c r="O194" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P194" s="31"/>
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>114</v>
       </c>
@@ -9280,8 +9587,11 @@
       <c r="O195" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P195" s="32">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>115</v>
       </c>
@@ -9325,8 +9635,11 @@
       <c r="O196" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P196" s="31">
+        <v>45829</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>116</v>
       </c>
@@ -9355,8 +9668,9 @@
       <c r="O197" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P197" s="32"/>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>117</v>
       </c>
@@ -9398,8 +9712,11 @@
       <c r="O198" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P198" s="31">
+        <v>45853</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>118</v>
       </c>
@@ -9426,8 +9743,9 @@
       <c r="O199" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P199" s="32"/>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>119</v>
       </c>
@@ -9455,8 +9773,9 @@
       <c r="O200" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P200" s="31"/>
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>120</v>
       </c>
@@ -9483,8 +9802,9 @@
       <c r="O201" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P201" s="32"/>
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>1</v>
       </c>
@@ -9526,8 +9846,11 @@
       <c r="O202" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P202" s="34">
+        <v>33708</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
         <v>2</v>
       </c>
@@ -9569,8 +9892,11 @@
       <c r="O203" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P203" s="35">
+        <v>45315</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
         <v>3</v>
       </c>
@@ -9606,8 +9932,9 @@
       <c r="O204" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P204" s="34"/>
+    </row>
+    <row r="205" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>4</v>
       </c>
@@ -9649,8 +9976,11 @@
       <c r="O205" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P205" s="34">
+        <v>43054</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
         <v>5</v>
       </c>
@@ -9689,8 +10019,11 @@
       <c r="O206" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P206" s="35">
+        <v>45832</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>6</v>
       </c>
@@ -9734,8 +10067,11 @@
       <c r="O207" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P207" s="34">
+        <v>46067</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A208" s="5">
         <v>7</v>
       </c>
@@ -9773,8 +10109,9 @@
       <c r="O208" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P208" s="34"/>
+    </row>
+    <row r="209" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
         <v>8</v>
       </c>
@@ -9804,8 +10141,9 @@
       <c r="O209" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P209" s="6"/>
+    </row>
+    <row r="210" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>9</v>
       </c>
@@ -9847,8 +10185,11 @@
       <c r="O210" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P210" s="34">
+        <v>46368</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>10</v>
       </c>
@@ -9887,8 +10228,11 @@
       <c r="O211" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P211" s="34">
+        <v>42983</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
         <v>11</v>
       </c>
@@ -9930,8 +10274,11 @@
       <c r="O212" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P212" s="35">
+        <v>25045</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>12</v>
       </c>
@@ -9973,8 +10320,11 @@
       <c r="O213" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P213" s="34">
+        <v>43158</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>13</v>
       </c>
@@ -10013,8 +10363,11 @@
       <c r="O214" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P214" s="34">
+        <v>43304</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
         <v>14</v>
       </c>
@@ -10051,8 +10404,11 @@
       <c r="O215" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P215" s="35">
+        <v>43902</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>15</v>
       </c>
@@ -10091,8 +10447,11 @@
       <c r="O216" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P216" s="34">
+        <v>42571</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>16</v>
       </c>
@@ -10134,8 +10493,11 @@
       <c r="O217" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P217" s="34">
+        <v>43266</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
         <v>17</v>
       </c>
@@ -10169,8 +10531,9 @@
       <c r="O218" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P218" s="35"/>
+    </row>
+    <row r="219" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>18</v>
       </c>
@@ -10214,8 +10577,11 @@
       <c r="O219" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P219" s="34">
+        <v>42640</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A220" s="7">
         <v>19</v>
       </c>
@@ -10254,8 +10620,11 @@
       <c r="O220" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P220" s="36">
+        <v>43592</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>20</v>
       </c>
@@ -10298,6 +10667,9 @@
       <c r="N221" s="26"/>
       <c r="O221" s="5">
         <v>3</v>
+      </c>
+      <c r="P221" s="34">
+        <v>43117</v>
       </c>
     </row>
   </sheetData>
